--- a/AAII_Financials/Yearly/BH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BH_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>55800</v>
+        <v>56400</v>
       </c>
       <c r="E14" s="3">
-        <v>25100</v>
+        <v>25500</v>
       </c>
       <c r="F14" s="3">
-        <v>-31300</v>
+        <v>-29100</v>
       </c>
       <c r="G14" s="3">
         <v>82900</v>
